--- a/Team-Data/2008-09/12-1-2008-09.xlsx
+++ b/Team-Data/2008-09/12-1-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,22 +806,22 @@
         <v>1.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE2" t="n">
         <v>10</v>
       </c>
       <c r="AF2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG2" t="n">
         <v>7</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ2" t="n">
         <v>18</v>
@@ -775,10 +842,10 @@
         <v>20</v>
       </c>
       <c r="AP2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR2" t="n">
         <v>16</v>
@@ -790,10 +857,10 @@
         <v>16</v>
       </c>
       <c r="AU2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
         <v>19</v>
@@ -805,13 +872,13 @@
         <v>16</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
         <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -858,70 +925,70 @@
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>35.7</v>
+        <v>35.3</v>
       </c>
       <c r="J3" t="n">
         <v>75.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.471</v>
+        <v>0.466</v>
       </c>
       <c r="L3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M3" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.349</v>
+        <v>0.337</v>
       </c>
       <c r="O3" t="n">
         <v>22.4</v>
       </c>
       <c r="P3" t="n">
-        <v>29.1</v>
+        <v>29.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.771</v>
+        <v>0.756</v>
       </c>
       <c r="R3" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S3" t="n">
-        <v>32.7</v>
+        <v>32.2</v>
       </c>
       <c r="T3" t="n">
-        <v>42.9</v>
+        <v>42.5</v>
       </c>
       <c r="U3" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="V3" t="n">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
       <c r="W3" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
         <v>5.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.7</v>
+        <v>23.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>99.2</v>
+        <v>98.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,64 +1003,64 @@
         <v>16</v>
       </c>
       <c r="AI3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AM3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AN3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AO3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP3" t="n">
         <v>4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AR3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
         <v>11</v>
       </c>
       <c r="AV3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
         <v>5</v>
       </c>
       <c r="AX3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY3" t="n">
         <v>6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
         <v>3</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -1025,37 +1092,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
         <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>0.353</v>
+        <v>0.313</v>
       </c>
       <c r="H4" t="n">
         <v>48.3</v>
       </c>
       <c r="I4" t="n">
-        <v>32.4</v>
+        <v>32.1</v>
       </c>
       <c r="J4" t="n">
-        <v>74.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.433</v>
+        <v>0.431</v>
       </c>
       <c r="L4" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="M4" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.344</v>
+        <v>0.333</v>
       </c>
       <c r="O4" t="n">
         <v>19.4</v>
@@ -1064,7 +1131,7 @@
         <v>25.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="R4" t="n">
         <v>10.9</v>
@@ -1076,37 +1143,37 @@
         <v>38.5</v>
       </c>
       <c r="U4" t="n">
-        <v>17.6</v>
+        <v>16.9</v>
       </c>
       <c r="V4" t="n">
-        <v>15.6</v>
+        <v>15.9</v>
       </c>
       <c r="W4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="X4" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>89.3</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AE4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
         <v>22</v>
@@ -1115,7 +1182,7 @@
         <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1124,46 +1191,46 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR4" t="n">
         <v>19</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>20</v>
       </c>
       <c r="AS4" t="n">
         <v>29</v>
       </c>
       <c r="AT4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU4" t="n">
         <v>29</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>28</v>
       </c>
       <c r="AV4" t="n">
         <v>22</v>
       </c>
       <c r="AW4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
         <v>30</v>
@@ -1172,13 +1239,13 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -1207,61 +1274,61 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
         <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>0.438</v>
+        <v>0.471</v>
       </c>
       <c r="H5" t="n">
         <v>48</v>
       </c>
       <c r="I5" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J5" t="n">
-        <v>84.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.43</v>
+        <v>0.434</v>
       </c>
       <c r="L5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.36</v>
+        <v>0.362</v>
       </c>
       <c r="O5" t="n">
-        <v>19.1</v>
+        <v>19.9</v>
       </c>
       <c r="P5" t="n">
-        <v>23.5</v>
+        <v>24.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.805</v>
       </c>
       <c r="R5" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S5" t="n">
-        <v>30.6</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="U5" t="n">
-        <v>18.7</v>
+        <v>19.2</v>
       </c>
       <c r="V5" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="W5" t="n">
         <v>8.4</v>
@@ -1270,61 +1337,61 @@
         <v>5.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.3</v>
+        <v>22.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>97.5</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.4</v>
+        <v>-2.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AF5" t="n">
         <v>18</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
         <v>14</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO5" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR5" t="n">
         <v>6</v>
@@ -1333,13 +1400,13 @@
         <v>14</v>
       </c>
       <c r="AT5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
         <v>24</v>
       </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
         <v>6</v>
@@ -1348,20 +1415,20 @@
         <v>17</v>
       </c>
       <c r="AY5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BA5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC5" t="n">
         <v>22</v>
       </c>
-      <c r="BB5" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>23</v>
-      </c>
       <c r="BD5" t="n">
         <v>10</v>
       </c>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -1389,100 +1456,100 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
         <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.875</v>
+        <v>0.824</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>38.7</v>
+        <v>38.1</v>
       </c>
       <c r="J6" t="n">
-        <v>80</v>
+        <v>79.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.484</v>
+        <v>0.481</v>
       </c>
       <c r="L6" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.346</v>
+        <v>0.339</v>
       </c>
       <c r="O6" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="P6" t="n">
-        <v>26.3</v>
+        <v>26.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.772</v>
+        <v>0.769</v>
       </c>
       <c r="R6" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="S6" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T6" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="U6" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="V6" t="n">
-        <v>12.4</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
         <v>7.4</v>
       </c>
       <c r="X6" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>104.8</v>
+        <v>103.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.9</v>
+        <v>10.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG6" t="n">
         <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ6" t="n">
         <v>16</v>
@@ -1494,49 +1561,49 @@
         <v>10</v>
       </c>
       <c r="AM6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO6" t="n">
         <v>6</v>
       </c>
       <c r="AP6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
         <v>12</v>
       </c>
       <c r="AR6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AV6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW6" t="n">
         <v>16</v>
       </c>
       <c r="AX6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB6" t="n">
         <v>4</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>2.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF7" t="n">
         <v>15</v>
@@ -1664,10 +1731,10 @@
         <v>10</v>
       </c>
       <c r="AI7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK7" t="n">
         <v>20</v>
@@ -1679,13 +1746,13 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO7" t="n">
         <v>18</v>
       </c>
       <c r="AP7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ7" t="n">
         <v>5</v>
@@ -1700,13 +1767,13 @@
         <v>2</v>
       </c>
       <c r="AU7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV7" t="n">
         <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX7" t="n">
         <v>16</v>
@@ -1721,7 +1788,7 @@
         <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -1831,16 +1898,16 @@
         <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH8" t="n">
         <v>16</v>
@@ -1855,13 +1922,13 @@
         <v>11</v>
       </c>
       <c r="AL8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM8" t="n">
         <v>17</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1876,10 +1943,10 @@
         <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
@@ -1894,7 +1961,7 @@
         <v>7</v>
       </c>
       <c r="AY8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ8" t="n">
         <v>21</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -2013,34 +2080,34 @@
         <v>0.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
         <v>10</v>
       </c>
       <c r="AF9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG9" t="n">
         <v>7</v>
       </c>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ9" t="n">
         <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL9" t="n">
         <v>16</v>
       </c>
       <c r="AM9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN9" t="n">
         <v>7</v>
@@ -2049,22 +2116,22 @@
         <v>7</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR9" t="n">
         <v>16</v>
       </c>
       <c r="AS9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT9" t="n">
         <v>18</v>
       </c>
       <c r="AU9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AV9" t="n">
         <v>5</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -2117,61 +2184,61 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
         <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>0.278</v>
+        <v>0.294</v>
       </c>
       <c r="H10" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
       <c r="I10" t="n">
         <v>38.4</v>
       </c>
       <c r="J10" t="n">
-        <v>86.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="K10" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M10" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.307</v>
+        <v>0.308</v>
       </c>
       <c r="O10" t="n">
-        <v>23.7</v>
+        <v>22.4</v>
       </c>
       <c r="P10" t="n">
-        <v>31.6</v>
+        <v>30.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.752</v>
+        <v>0.736</v>
       </c>
       <c r="R10" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="S10" t="n">
-        <v>29.4</v>
+        <v>29.7</v>
       </c>
       <c r="T10" t="n">
-        <v>42.8</v>
+        <v>43.2</v>
       </c>
       <c r="U10" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="V10" t="n">
-        <v>14.8</v>
+        <v>15.1</v>
       </c>
       <c r="W10" t="n">
         <v>8.199999999999999</v>
@@ -2180,37 +2247,37 @@
         <v>7.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>25.6</v>
+        <v>24.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>106</v>
+        <v>104.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4.3</v>
+        <v>-4.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF10" t="n">
         <v>24</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>26</v>
       </c>
       <c r="AG10" t="n">
         <v>24</v>
       </c>
       <c r="AH10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI10" t="n">
         <v>3</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>4</v>
       </c>
       <c r="AJ10" t="n">
         <v>3</v>
@@ -2219,31 +2286,31 @@
         <v>19</v>
       </c>
       <c r="AL10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AM10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP10" t="n">
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AR10" t="n">
         <v>3</v>
       </c>
       <c r="AS10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
         <v>22</v>
@@ -2258,10 +2325,10 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>3.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
@@ -2398,34 +2465,34 @@
         <v>17</v>
       </c>
       <c r="AK11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
         <v>14</v>
       </c>
       <c r="AM11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN11" t="n">
         <v>14</v>
       </c>
       <c r="AO11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AP11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
         <v>2</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
         <v>5</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AU11" t="n">
         <v>26</v>
@@ -2440,7 +2507,7 @@
         <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>0.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE12" t="n">
         <v>22</v>
@@ -2568,16 +2635,16 @@
         <v>20</v>
       </c>
       <c r="AG12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI12" t="n">
         <v>7</v>
       </c>
       <c r="AJ12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK12" t="n">
         <v>18</v>
@@ -2586,7 +2653,7 @@
         <v>9</v>
       </c>
       <c r="AM12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN12" t="n">
         <v>15</v>
@@ -2613,7 +2680,7 @@
         <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW12" t="n">
         <v>25</v>
@@ -2622,16 +2689,16 @@
         <v>4</v>
       </c>
       <c r="AY12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ12" t="n">
         <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC12" t="n">
         <v>16</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -2741,13 +2808,13 @@
         <v>-8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
       </c>
       <c r="AF13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG13" t="n">
         <v>28</v>
@@ -2765,13 +2832,13 @@
         <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM13" t="n">
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO13" t="n">
         <v>29</v>
@@ -2792,7 +2859,7 @@
         <v>22</v>
       </c>
       <c r="AU13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV13" t="n">
         <v>18</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
+        <v>15</v>
+      </c>
+      <c r="E14" t="n">
         <v>14</v>
-      </c>
-      <c r="E14" t="n">
-        <v>13</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.929</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>41.1</v>
+        <v>40.8</v>
       </c>
       <c r="J14" t="n">
-        <v>88.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="K14" t="n">
         <v>0.466</v>
@@ -2872,61 +2939,61 @@
         <v>6.6</v>
       </c>
       <c r="M14" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.362</v>
+        <v>0.375</v>
       </c>
       <c r="O14" t="n">
-        <v>19.9</v>
+        <v>19.6</v>
       </c>
       <c r="P14" t="n">
-        <v>26.4</v>
+        <v>25.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.756</v>
+        <v>0.76</v>
       </c>
       <c r="R14" t="n">
-        <v>14.1</v>
+        <v>13.7</v>
       </c>
       <c r="S14" t="n">
-        <v>33.2</v>
+        <v>33.7</v>
       </c>
       <c r="T14" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="U14" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="V14" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W14" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="X14" t="n">
         <v>6.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.6</v>
+        <v>107.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>1</v>
@@ -2935,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
@@ -2944,25 +3011,25 @@
         <v>2</v>
       </c>
       <c r="AK14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL14" t="n">
         <v>13</v>
       </c>
       <c r="AM14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO14" t="n">
         <v>12</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AP14" t="n">
         <v>11</v>
       </c>
-      <c r="AO14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>7</v>
-      </c>
       <c r="AQ14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR14" t="n">
         <v>2</v>
@@ -2974,16 +3041,16 @@
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY14" t="n">
         <v>12</v>
@@ -2992,7 +3059,7 @@
         <v>5</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -3105,19 +3172,19 @@
         <v>-6.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI15" t="n">
         <v>23</v>
@@ -3126,7 +3193,7 @@
         <v>23</v>
       </c>
       <c r="AK15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL15" t="n">
         <v>28</v>
@@ -3141,13 +3208,13 @@
         <v>19</v>
       </c>
       <c r="AP15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ15" t="n">
         <v>19</v>
       </c>
       <c r="AR15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS15" t="n">
         <v>16</v>
@@ -3159,7 +3226,7 @@
         <v>30</v>
       </c>
       <c r="AV15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW15" t="n">
         <v>10</v>
@@ -3171,7 +3238,7 @@
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA15" t="n">
         <v>14</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -3209,136 +3276,136 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="n">
         <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="H16" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>37.1</v>
+        <v>36.5</v>
       </c>
       <c r="J16" t="n">
-        <v>82.2</v>
+        <v>81.2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.452</v>
+        <v>0.45</v>
       </c>
       <c r="L16" t="n">
         <v>7.3</v>
       </c>
       <c r="M16" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O16" t="n">
-        <v>17.6</v>
+        <v>16.9</v>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.754</v>
+        <v>0.742</v>
       </c>
       <c r="R16" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="S16" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="T16" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="U16" t="n">
-        <v>20.8</v>
+        <v>20.2</v>
       </c>
       <c r="V16" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="W16" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X16" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>21.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>99.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="AC16" t="n">
         <v>1.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AF16" t="n">
         <v>18</v>
       </c>
       <c r="AG16" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AH16" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AJ16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM16" t="n">
         <v>4</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AO16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR16" t="n">
         <v>21</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>19</v>
       </c>
       <c r="AS16" t="n">
         <v>28</v>
       </c>
       <c r="AT16" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AU16" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AV16" t="n">
         <v>1</v>
@@ -3347,19 +3414,19 @@
         <v>4</v>
       </c>
       <c r="AX16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>9</v>
       </c>
-      <c r="AY16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>16</v>
-      </c>
       <c r="BA16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB16" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BC16" t="n">
         <v>12</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
         <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>0.389</v>
+        <v>0.368</v>
       </c>
       <c r="H17" t="n">
         <v>48.8</v>
       </c>
       <c r="I17" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="J17" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.427</v>
+        <v>0.429</v>
       </c>
       <c r="L17" t="n">
         <v>4.9</v>
@@ -3421,34 +3488,34 @@
         <v>14.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.345</v>
+        <v>0.349</v>
       </c>
       <c r="O17" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="P17" t="n">
-        <v>26.3</v>
+        <v>26</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="R17" t="n">
         <v>13.2</v>
       </c>
       <c r="S17" t="n">
-        <v>31.5</v>
+        <v>30.8</v>
       </c>
       <c r="T17" t="n">
-        <v>44.7</v>
+        <v>44</v>
       </c>
       <c r="U17" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V17" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="W17" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="X17" t="n">
         <v>3.5</v>
@@ -3457,28 +3524,28 @@
         <v>5.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="AB17" t="n">
         <v>95</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.8</v>
+        <v>-2.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG17" t="n">
         <v>22</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>21</v>
       </c>
       <c r="AH17" t="n">
         <v>2</v>
@@ -3487,43 +3554,43 @@
         <v>27</v>
       </c>
       <c r="AJ17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AM17" t="n">
         <v>26</v>
       </c>
       <c r="AN17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP17" t="n">
         <v>9</v>
       </c>
-      <c r="AP17" t="n">
-        <v>8</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR17" t="n">
         <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AT17" t="n">
         <v>5</v>
       </c>
       <c r="AU17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AW17" t="n">
         <v>28</v>
@@ -3532,13 +3599,13 @@
         <v>27</v>
       </c>
       <c r="AY17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ17" t="n">
         <v>29</v>
       </c>
       <c r="BA17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB17" t="n">
         <v>23</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -3573,118 +3640,118 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18" t="n">
-        <v>0.25</v>
+        <v>0.267</v>
       </c>
       <c r="H18" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I18" t="n">
-        <v>36.9</v>
+        <v>37.4</v>
       </c>
       <c r="J18" t="n">
-        <v>84.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.435</v>
+        <v>0.437</v>
       </c>
       <c r="L18" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="M18" t="n">
-        <v>15.8</v>
+        <v>15.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0.336</v>
+        <v>0.325</v>
       </c>
       <c r="O18" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P18" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.783</v>
+        <v>0.785</v>
       </c>
       <c r="R18" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S18" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T18" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U18" t="n">
-        <v>23.3</v>
+        <v>23.7</v>
       </c>
       <c r="V18" t="n">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="W18" t="n">
         <v>5.8</v>
       </c>
       <c r="X18" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="AA18" t="n">
         <v>20.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>97</v>
+        <v>97.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.4</v>
+        <v>-3</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="AE18" t="n">
         <v>26</v>
       </c>
       <c r="AF18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH18" t="n">
         <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL18" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AM18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO18" t="n">
         <v>21</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>22</v>
       </c>
       <c r="AP18" t="n">
         <v>23</v>
@@ -3693,37 +3760,37 @@
         <v>6</v>
       </c>
       <c r="AR18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS18" t="n">
         <v>21</v>
       </c>
       <c r="AT18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
         <v>29</v>
       </c>
       <c r="AX18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC18" t="n">
         <v>23</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
         <v>12</v>
@@ -3845,25 +3912,25 @@
         <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ19" t="n">
         <v>14</v>
       </c>
       <c r="AK19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM19" t="n">
         <v>8</v>
       </c>
       <c r="AN19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO19" t="n">
         <v>4</v>
@@ -3884,7 +3951,7 @@
         <v>20</v>
       </c>
       <c r="AU19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV19" t="n">
         <v>7</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -4015,13 +4082,13 @@
         <v>3.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE20" t="n">
         <v>12</v>
       </c>
       <c r="AF20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG20" t="n">
         <v>12</v>
@@ -4030,13 +4097,13 @@
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ20" t="n">
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL20" t="n">
         <v>6</v>
@@ -4048,13 +4115,13 @@
         <v>4</v>
       </c>
       <c r="AO20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>27</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR20" t="n">
         <v>27</v>
@@ -4066,7 +4133,7 @@
         <v>30</v>
       </c>
       <c r="AU20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV20" t="n">
         <v>8</v>
@@ -4081,7 +4148,7 @@
         <v>4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA20" t="n">
         <v>19</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -4197,10 +4264,10 @@
         <v>-2.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF21" t="n">
         <v>15</v>
@@ -4230,7 +4297,7 @@
         <v>8</v>
       </c>
       <c r="AO21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP21" t="n">
         <v>26</v>
@@ -4248,13 +4315,13 @@
         <v>6</v>
       </c>
       <c r="AU21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-11.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>29</v>
@@ -4391,7 +4458,7 @@
         <v>30</v>
       </c>
       <c r="AH22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
         <v>28</v>
@@ -4409,22 +4476,22 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP22" t="n">
         <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT22" t="n">
         <v>15</v>
@@ -4433,7 +4500,7 @@
         <v>27</v>
       </c>
       <c r="AV22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW22" t="n">
         <v>15</v>
@@ -4448,7 +4515,7 @@
         <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB22" t="n">
         <v>29</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -4483,88 +4550,88 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E23" t="n">
         <v>13</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>0.722</v>
+        <v>0.765</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="J23" t="n">
-        <v>78.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.447</v>
+        <v>0.449</v>
       </c>
       <c r="L23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="M23" t="n">
         <v>24.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0.33</v>
+        <v>0.338</v>
       </c>
       <c r="O23" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="P23" t="n">
-        <v>29.6</v>
+        <v>29.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.719</v>
+        <v>0.724</v>
       </c>
       <c r="R23" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="S23" t="n">
-        <v>32.4</v>
+        <v>32.9</v>
       </c>
       <c r="T23" t="n">
-        <v>43.1</v>
+        <v>43.3</v>
       </c>
       <c r="U23" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="V23" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="W23" t="n">
         <v>7.2</v>
       </c>
       <c r="X23" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>99.7</v>
+        <v>100.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="n">
         <v>4</v>
@@ -4573,16 +4640,16 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI23" t="n">
         <v>26</v>
       </c>
       <c r="AJ23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL23" t="n">
         <v>4</v>
@@ -4591,7 +4658,7 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AO23" t="n">
         <v>5</v>
@@ -4606,16 +4673,16 @@
         <v>21</v>
       </c>
       <c r="AS23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AT23" t="n">
         <v>7</v>
       </c>
       <c r="AU23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW23" t="n">
         <v>18</v>
@@ -4624,19 +4691,19 @@
         <v>2</v>
       </c>
       <c r="AY23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BC23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>-0.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF24" t="n">
         <v>20</v>
@@ -4755,16 +4822,16 @@
         <v>20</v>
       </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4773,7 +4840,7 @@
         <v>28</v>
       </c>
       <c r="AN24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO24" t="n">
         <v>28</v>
@@ -4794,19 +4861,19 @@
         <v>4</v>
       </c>
       <c r="AU24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW24" t="n">
         <v>21</v>
       </c>
       <c r="AX24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ24" t="n">
         <v>4</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>0.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>7</v>
@@ -4940,7 +5007,7 @@
         <v>16</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ25" t="n">
         <v>30</v>
@@ -4958,25 +5025,25 @@
         <v>6</v>
       </c>
       <c r="AO25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP25" t="n">
         <v>8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR25" t="n">
         <v>30</v>
       </c>
       <c r="AS25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT25" t="n">
         <v>24</v>
       </c>
       <c r="AU25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV25" t="n">
         <v>30</v>
@@ -4988,13 +5055,13 @@
         <v>14</v>
       </c>
       <c r="AY25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ25" t="n">
         <v>7</v>
       </c>
       <c r="BA25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB25" t="n">
         <v>6</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -5029,58 +5096,58 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E26" t="n">
         <v>12</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>0.706</v>
+        <v>0.667</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.6</v>
+        <v>36.2</v>
       </c>
       <c r="J26" t="n">
-        <v>78.5</v>
+        <v>78.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.466</v>
+        <v>0.459</v>
       </c>
       <c r="L26" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="N26" t="n">
         <v>0.414</v>
       </c>
       <c r="O26" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="P26" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.77</v>
+        <v>0.763</v>
       </c>
       <c r="R26" t="n">
         <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="T26" t="n">
-        <v>40.3</v>
+        <v>40.5</v>
       </c>
       <c r="U26" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V26" t="n">
         <v>13.1</v>
@@ -5089,46 +5156,46 @@
         <v>7.3</v>
       </c>
       <c r="X26" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="Y26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD26" t="n">
         <v>3</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>12</v>
       </c>
       <c r="AE26" t="n">
         <v>5</v>
       </c>
       <c r="AF26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG26" t="n">
         <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AI26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AJ26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL26" t="n">
         <v>3</v>
@@ -5140,13 +5207,13 @@
         <v>2</v>
       </c>
       <c r="AO26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR26" t="n">
         <v>5</v>
@@ -5176,13 +5243,13 @@
         <v>12</v>
       </c>
       <c r="BA26" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BB26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -5292,13 +5359,13 @@
         <v>1</v>
       </c>
       <c r="AE27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF27" t="n">
         <v>29</v>
       </c>
       <c r="AG27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH27" t="n">
         <v>8</v>
@@ -5313,7 +5380,7 @@
         <v>4</v>
       </c>
       <c r="AL27" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AM27" t="n">
         <v>20</v>
@@ -5337,7 +5404,7 @@
         <v>23</v>
       </c>
       <c r="AT27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU27" t="n">
         <v>9</v>
@@ -5355,7 +5422,7 @@
         <v>11</v>
       </c>
       <c r="AZ27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA27" t="n">
         <v>21</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>0.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE28" t="n">
         <v>12</v>
@@ -5483,16 +5550,16 @@
         <v>13</v>
       </c>
       <c r="AH28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ28" t="n">
         <v>26</v>
       </c>
       <c r="AK28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL28" t="n">
         <v>5</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
@@ -5522,10 +5589,10 @@
         <v>25</v>
       </c>
       <c r="AU28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW28" t="n">
         <v>30</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -5653,10 +5720,10 @@
         <v>-1.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF29" t="n">
         <v>15</v>
@@ -5665,10 +5732,10 @@
         <v>15</v>
       </c>
       <c r="AH29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ29" t="n">
         <v>24</v>
@@ -5689,7 +5756,7 @@
         <v>8</v>
       </c>
       <c r="AP29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5701,7 +5768,7 @@
         <v>15</v>
       </c>
       <c r="AT29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU29" t="n">
         <v>5</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>3.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>7</v>
@@ -5847,13 +5914,13 @@
         <v>9</v>
       </c>
       <c r="AH30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI30" t="n">
         <v>5</v>
       </c>
       <c r="AJ30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK30" t="n">
         <v>2</v>
@@ -5865,10 +5932,10 @@
         <v>29</v>
       </c>
       <c r="AN30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP30" t="n">
         <v>12</v>
@@ -5895,7 +5962,7 @@
         <v>3</v>
       </c>
       <c r="AX30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY30" t="n">
         <v>18</v>
@@ -5907,7 +5974,7 @@
         <v>6</v>
       </c>
       <c r="BB30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC30" t="n">
         <v>6</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6032,7 +6099,7 @@
         <v>9</v>
       </c>
       <c r="AI31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ31" t="n">
         <v>10</v>
@@ -6050,16 +6117,16 @@
         <v>30</v>
       </c>
       <c r="AO31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP31" t="n">
         <v>13</v>
       </c>
       <c r="AQ31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS31" t="n">
         <v>24</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-1-2008-09</t>
+          <t>2008-12-01</t>
         </is>
       </c>
     </row>
